--- a/output/pdf_financials_xlsx/SLG.xlsx
+++ b/output/pdf_financials_xlsx/SLG.xlsx
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.4e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.183966</v>
+        <v>-0.183966</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.8340649999999999</v>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.4e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.183966</v>
+        <v>-0.183966</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.8340649999999999</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.4e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.183966</v>
+        <v>-0.183966</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.8340649999999999</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-1.22644</v>
+        <v>1.22644</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.4e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.183966</v>
+        <v>-0.183966</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.8340649999999999</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.4e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.183966</v>
+        <v>-0.183966</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.8340649999999999</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4537,25 +4537,25 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.767286</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.099324</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.371813</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.625748</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.817014</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.614889</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.915051</v>
       </c>
     </row>
     <row r="119">
@@ -13355,7 +13355,11 @@
           <t>Paid exploration and evaluation expenditures 4 $</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -14307,7 +14311,11 @@
           <t>Exploration and evaluation expenditures 4</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -15576,7 +15584,11 @@
           <t>Paid exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -20934,10 +20946,10 @@
         </is>
       </c>
       <c r="E261" s="5" t="n">
-        <v>1.4e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>0.183966</v>
+        <v>-0.183966</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SLG.xlsx
+++ b/output/pdf_financials_xlsx/SLG.xlsx
@@ -739,22 +739,22 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.8340649999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>1.604203</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.060826</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.567706</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.404017</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.388747</v>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
@@ -775,22 +775,22 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.8340649999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-1.604203</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-1.060826</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.567706</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.404017</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-0.388747</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -1652,31 +1652,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.278486</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.385391</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.72881</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.6903550000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.00726</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.5874</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.061981</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.031574</v>
       </c>
     </row>
     <row r="35">
@@ -1720,31 +1720,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.278486</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.385391</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.72881</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.6903550000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.00726</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.5874</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.061981</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.031574</v>
       </c>
     </row>
     <row r="37">
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.879201</v>
+        <v>0.150391</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.6903550000000001</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.00726</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.5874</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.061981</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.26217</v>
+        <v>0.230596</v>
       </c>
     </row>
     <row r="49">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">

--- a/output/pdf_financials_xlsx/SLG.xlsx
+++ b/output/pdf_financials_xlsx/SLG.xlsx
@@ -4271,13 +4271,13 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.025588</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.046912</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.035568</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -14075,7 +14075,11 @@
           <t>Accretion 5</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
